--- a/docs/DOH_뷰별_측정가능표.xlsx
+++ b/docs/DOH_뷰별_측정가능표.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="진단 17 × 뷰" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="진단 18 × 뷰" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="측정 42 × 뷰" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'진단 17 × 뷰'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'진단 18 × 뷰'!$A$1:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'측정 42 × 뷰'!$A$1:$G$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>힙 슬라이드 과다</t>
+          <t>어드레스 어깨 기울기 부족</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -655,14 +655,14 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>골반 좌우 이동</t>
+          <t>어깨선 좌우 기울기 — 각도를 내려면 어깨너비가 필요한데 측면에선 깊이축</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>행잉백</t>
+          <t>힙 슬라이드 과다</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -677,36 +677,36 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>임팩트 좌우 체중 잔류</t>
+          <t>골반 좌우 이동</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>자세 무너짐 (백스윙)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>✕ 안 나옴</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>✅ 가능</t>
+          <t>행잉백</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>✅ 가능</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>✕ 안 나옴</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>척추 앞숙임 변화(시상면) — 정면에선 깊이축</t>
+          <t>임팩트 좌우 체중 잔류</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>일어남 (임팩트)</t>
+          <t>자세 무너짐 (백스윙)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -721,19 +721,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>상동</t>
+          <t>척추 앞숙임 변화(시상면) — 정면에선 깊이축</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>치킨윙 경향</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>✅ 가능</t>
+          <t>일어남 (임팩트)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>✕ 안 나옴</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -743,14 +743,14 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>3D 관절 굽힘각 — 뷰 무관 강건</t>
+          <t>상동</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>플라잉 엘보 경향</t>
+          <t>치킨윙 경향</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -765,14 +765,14 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>팔꿈치 높이(수직) — 양쪽 보임</t>
+          <t>3D 관절 굽힘각 — 뷰 무관 강건</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>오버스윙 경향</t>
+          <t>플라잉 엘보 경향</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -787,14 +787,14 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>리드팔 수직각 — 양쪽</t>
+          <t>팔꿈치 높이(수직) — 양쪽 보임</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상체 회전 부족</t>
+          <t>오버스윙 경향</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>3D 복원 회전 — 뷰 무관 (절대각 스케일 주의)</t>
+          <t>리드팔 수직각 — 양쪽</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>X-Factor 이상</t>
+          <t>상체 회전 부족</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>상동</t>
+          <t>3D 복원 회전 — 뷰 무관 (절대각 스케일 주의)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>트레일 무릎 펴짐</t>
+          <t>X-Factor 이상</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -853,14 +853,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>3D 무릎 굽힘각</t>
+          <t>상동</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>머리 상하 출렁</t>
+          <t>트레일 무릎 펴짐</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -875,14 +875,14 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>수직 이동 — 양쪽</t>
+          <t>3D 무릎 굽힘각</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>템포 이상</t>
+          <t>머리 상하 출렁</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -897,19 +897,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>시간 산술 — 뷰 무관</t>
+          <t>수직 이동 — 양쪽</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>얼리 익스텐션</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>◐ 저신뢰</t>
+          <t>템포 이상</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>✅ 가능</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -919,66 +919,88 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>측면=tush line 이탈(볼쪽 축이 화면 안이라 측정 가능) / 정면=벨트버클 상승분만 부분 포착</t>
+          <t>시간 산술 — 뷰 무관</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>얼리 익스텐션</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>◐ 저신뢰</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>✅ 가능</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>측면=tush line 이탈(볼쪽 축이 화면 안이라 측정 가능) / 정면=벨트버클 상승분만 부분 포착</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>오버더톱 경향</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>✕ 안 나옴</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>✅ 가능</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>✕ 안 나옴</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>✅ 가능</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>손이 볼쪽으로 던져짐 — 측면에선 화면 안 축(깊이 아님)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>요약: 정면(FO) = 진단 13/17 가능 · 측면(DTL) = 12/17 + 저신뢰 0 = 최대 12/17.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>핵심: 좌우 계열(스웨이·리버스·슬라이드·행잉백) 5개=정면 전용 / 앞뒤 계열(자세각·일어남·얼리익스텐션·OTT) 4개=측면 우세. ※ 검수3차 정정: 측면에서 '앞뒤'는 화면 안 축(깊이축은 타깃선) → tush line·손깊이는 저신뢰가 아니라 정상 측정. 얼리익스텐션은 정면에서도 벨트버클 상승분으로 부분 포착.</t>
+          <t>요약: 정면(FO) = 진단 14/17 가능 · 측면(DTL) = 12/17 + 저신뢰 0 = 최대 12/17.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>이 표는 엔진에 이미 내장된 자동 처리의 문서화 — 안 나오는 항목은 값이 null이 되고 화면에 '판정불가/측정 불가'로 뜸(지어내지 않음).</t>
+          <t>핵심: 좌우 계열(스웨이·리버스·슬라이드·행잉백) 5개=정면 전용 / 앞뒤 계열(자세각·일어남·얼리익스텐션·OTT) 4개=측면 우세. ※ 검수3차 정정: 측면에서 '앞뒤'는 화면 안 축(깊이축은 타깃선) → tush line·손깊이는 저신뢰가 아니라 정상 측정. 얼리익스텐션은 정면에서도 벨트버클 상승분으로 부분 포착.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>이 표는 엔진에 이미 내장된 자동 처리의 문서화 — 안 나오는 항목은 값이 null이 되고 화면에 '판정불가/측정 불가'로 뜸(지어내지 않음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>권장: 제대로 보려면 정면+측면 각 1회(같은 스윙 아니어도 됨). 한 번만 찍는다면 — 회전·팔·무릎은 어느 쪽이든 나오므로, 보고 싶은 결함 쪽 각도로.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D18"/>
+  <autoFilter ref="A1:D19"/>
   <mergeCells count="4">
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1605,14 +1627,14 @@
           <t>✕ 안 나옴</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>안 됨</t>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>됨</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>전두면</t>
+          <t>전두면 — 높이차(수직)는 양쪽 화면 안이지만 각도의 분모인 어깨너비가 측면에선 깊이축이라 신뢰불가 → 정면 전용(VF008)</t>
         </is>
       </c>
     </row>
